--- a/Parte I/resultados/tablas/analisis_exploratorio_pregunta_1.xlsx
+++ b/Parte I/resultados/tablas/analisis_exploratorio_pregunta_1.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>indicador</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -529,27 +517,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tipo_dato</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>valores_faltantes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>valores_infinitos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>valores_unicos</t>
         </is>
@@ -696,42 +684,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>media</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>desviacion_estandar</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>minimo</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>maximo</t>
         </is>
@@ -1652,22 +1640,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rho_spearman</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>valor_p</t>
         </is>
@@ -1778,42 +1766,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fila_original</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ndvi_med</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>evi_med</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ndre_med</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gli_med</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>height_med</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>motivo_revision</t>
         </is>
